--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_41.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3232739.085308719</v>
+        <v>3269097.131615935</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117083638</v>
+        <v>603.5370117079616</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117083638</v>
+        <v>603.5370117079616</v>
       </c>
     </row>
     <row r="11">
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>292.2764940197005</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>374</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -799,10 +799,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>190.3279297232695</v>
       </c>
       <c r="Y3" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -909,10 +909,10 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
-        <v>5.608919435675552</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>133.6519859716245</v>
@@ -1024,22 +1024,22 @@
         <v>62.48881128536601</v>
       </c>
       <c r="T6" t="n">
-        <v>4.473444462796863</v>
+        <v>108.42732792751</v>
       </c>
       <c r="U6" t="n">
-        <v>374</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X6" t="n">
+        <v>19.86273944538755</v>
+      </c>
+      <c r="Y6" t="n">
         <v>374</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>307.6657890022911</v>
       </c>
     </row>
     <row r="7">
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>374</v>
+        <v>326.5695244157589</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>77.6647646547211</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1261,13 +1261,13 @@
         <v>62.48881128536601</v>
       </c>
       <c r="T9" t="n">
-        <v>374</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
         <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S11" t="n">
         <v>142.3350019731772</v>
@@ -1422,7 +1422,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U11" t="n">
-        <v>328.5712507480957</v>
+        <v>328.1106633827815</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
         <v>26.93768689770263</v>
@@ -1498,7 +1498,7 @@
         <v>131.8202263797057</v>
       </c>
       <c r="T12" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
         <v>79.16168051490371</v>
@@ -1507,13 +1507,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>272.4545553273606</v>
       </c>
       <c r="Y12" t="n">
-        <v>251.9832086481073</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237.1483725282995</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>213.6917283274922</v>
       </c>
       <c r="D15" t="n">
         <v>347.9376868977026</v>
@@ -1693,7 +1693,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>3.99961134672543</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
@@ -1805,7 +1805,7 @@
         <v>291.4220612627038</v>
       </c>
       <c r="Q16" t="n">
-        <v>352.895266425598</v>
+        <v>352.0570205760006</v>
       </c>
       <c r="R16" t="n">
         <v>377.7099312598395</v>
@@ -1851,7 +1851,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G17" t="n">
         <v>81.3744577141519</v>
@@ -1860,7 +1860,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
         <v>40.09991244551929</v>
@@ -1930,13 +1930,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H18" t="n">
-        <v>4.021973978873973</v>
+        <v>177.6137898608469</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
         <v>131.8202263797057</v>
       </c>
       <c r="T18" t="n">
-        <v>254.9671660051473</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U18" t="n">
         <v>79.16168051490371</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
@@ -2045,7 +2045,7 @@
         <v>352.895266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>376.871685410242</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
         <v>30.56285675203577</v>
@@ -2091,7 +2091,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H20" t="n">
         <v>72.84688483418068</v>
@@ -2158,22 +2158,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D21" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2206,22 +2206,22 @@
         <v>180.333570877285</v>
       </c>
       <c r="S21" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T21" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>252.7534963968766</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
         <v>78.39139276613435</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2276,16 +2276,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P22" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q22" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C24" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>3.999611346725456</v>
@@ -2449,16 +2449,16 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>252.7534963968768</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
         <v>78.39139276613435</v>
@@ -2513,7 +2513,7 @@
         <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627037</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
@@ -2522,7 +2522,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>142.3350019731772</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>158.5198244189525</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
         <v>21.67209722191262</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>501.333570877285</v>
@@ -2686,10 +2686,10 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490372</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V27" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
         <v>111.3731429098285</v>
@@ -2698,7 +2698,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481077</v>
       </c>
     </row>
     <row r="28">
@@ -2741,7 +2741,7 @@
         <v>10.3217920922054</v>
       </c>
       <c r="M28" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N28" t="n">
         <v>155.2579933044718</v>
@@ -2756,7 +2756,7 @@
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>376.8716854102422</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S28" t="n">
         <v>30.56285675203577</v>
@@ -2802,10 +2802,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H29" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>142.3350019731772</v>
@@ -2881,10 +2881,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>98.96287911935116</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,16 +2914,16 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
-        <v>180.333570877285</v>
+        <v>275.2968386499106</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V30" t="n">
         <v>414.5106671915202</v>
@@ -2932,7 +2932,7 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
         <v>78.39139276613435</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M31" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N31" t="n">
         <v>155.2579933044718</v>
@@ -2987,13 +2987,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S31" t="n">
         <v>30.56285675203577</v>
@@ -3039,10 +3039,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H32" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S32" t="n">
         <v>142.3350019731772</v>
@@ -3106,22 +3106,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>213.6917283274922</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,19 +3151,19 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T33" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V33" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
         <v>111.3731429098285</v>
@@ -3172,7 +3172,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481076</v>
       </c>
     </row>
     <row r="34">
@@ -3212,25 +3212,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M34" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N34" t="n">
-        <v>154.4197474548741</v>
+        <v>155.2579933044718</v>
       </c>
       <c r="O34" t="n">
         <v>231.765039488851</v>
       </c>
       <c r="P34" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q34" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S34" t="n">
         <v>30.56285675203577</v>
@@ -3276,13 +3276,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H35" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3349,16 +3349,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G36" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3388,28 +3388,28 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
-        <v>275.296838649911</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>131.8202263797056</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T36" t="n">
-        <v>81.3753501231742</v>
+        <v>176.3386178957999</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V36" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,16 +3461,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090246903</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T38" t="n">
         <v>259.6218731858503</v>
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D39" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>3.999611346725456</v>
@@ -3640,13 +3640,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>284.9649587918016</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3707,7 +3707,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090247624</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3817,10 +3817,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>21.67209722191262</v>
@@ -3832,7 +3832,7 @@
         <v>3.999611346725456</v>
       </c>
       <c r="H42" t="n">
-        <v>98.98524175149973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3871,19 +3871,19 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V42" t="n">
-        <v>93.51066719152016</v>
+        <v>188.4739349641459</v>
       </c>
       <c r="W42" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3938,13 +3938,13 @@
         <v>291.4220612627037</v>
       </c>
       <c r="Q43" t="n">
-        <v>352.895266425598</v>
+        <v>352.0570205760006</v>
       </c>
       <c r="R43" t="n">
         <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,10 +3987,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H44" t="n">
-        <v>73.30747219949504</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4054,10 +4054,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D45" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
@@ -4066,10 +4066,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H45" t="n">
-        <v>177.6137898608472</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,16 +4099,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4172,13 +4172,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S46" t="n">
         <v>30.56285675203577</v>
@@ -4321,25 +4321,25 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L2" t="n">
-        <v>464.2419149748744</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="M2" t="n">
-        <v>834.5019149748744</v>
+        <v>1192.338330351759</v>
       </c>
       <c r="N2" t="n">
-        <v>1204.761914974874</v>
+        <v>1192.338330351759</v>
       </c>
       <c r="O2" t="n">
-        <v>1204.761914974874</v>
+        <v>1192.338330351759</v>
       </c>
       <c r="P2" t="n">
-        <v>1262.853806841132</v>
+        <v>1250.430222218017</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.13396963146437</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="C3" t="n">
-        <v>33.13396963146437</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="D3" t="n">
-        <v>33.13396963146437</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="E3" t="n">
-        <v>33.13396963146437</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="F3" t="n">
-        <v>33.13396963146437</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="G3" t="n">
-        <v>33.13396963146437</v>
+        <v>578.2064886541781</v>
       </c>
       <c r="H3" t="n">
-        <v>33.13396963146437</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="I3" t="n">
         <v>33.13396963146437</v>
@@ -4430,22 +4430,22 @@
         <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>856.1102823049354</v>
+        <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>478.3325045271575</v>
+        <v>1146.622528526128</v>
       </c>
       <c r="V3" t="n">
-        <v>463.6752649397635</v>
+        <v>1131.965288938734</v>
       </c>
       <c r="W3" t="n">
-        <v>430.9751205864013</v>
+        <v>1099.265144585372</v>
       </c>
       <c r="X3" t="n">
-        <v>410.9117474092422</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="Y3" t="n">
-        <v>33.13396963146437</v>
+        <v>907.0147105214633</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>218.6183178716313</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="C4" t="n">
-        <v>344.620323690067</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="D4" t="n">
-        <v>457.9394678150671</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="E4" t="n">
-        <v>575.7683720264802</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="F4" t="n">
-        <v>700.1293446184156</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="G4" t="n">
-        <v>853.7180055872682</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="H4" t="n">
-        <v>1024.853581566338</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="I4" t="n">
-        <v>1251.462556240126</v>
+        <v>931.1888901887032</v>
       </c>
       <c r="J4" t="n">
         <v>1251.462556240126</v>
@@ -4509,22 +4509,22 @@
         <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>106.8609802053391</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U4" t="n">
-        <v>106.8609802053391</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V4" t="n">
-        <v>106.8609802053391</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="W4" t="n">
-        <v>106.8609802053391</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="X4" t="n">
-        <v>106.8609802053391</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="Y4" t="n">
-        <v>106.8609802053391</v>
+        <v>704.5799155149155</v>
       </c>
     </row>
     <row r="5">
@@ -4552,7 +4552,7 @@
         <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.92</v>
+        <v>394.6673863086054</v>
       </c>
       <c r="C6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T6" t="n">
-        <v>1143.60646374105</v>
+        <v>1185.141459475101</v>
       </c>
       <c r="U6" t="n">
-        <v>765.8286859632726</v>
+        <v>1184.943554628714</v>
       </c>
       <c r="V6" t="n">
-        <v>751.1714463758785</v>
+        <v>1170.28631504132</v>
       </c>
       <c r="W6" t="n">
-        <v>718.4713020225164</v>
+        <v>792.5085372635424</v>
       </c>
       <c r="X6" t="n">
-        <v>340.6935242447386</v>
+        <v>772.4451640863832</v>
       </c>
       <c r="Y6" t="n">
-        <v>29.92</v>
+        <v>394.6673863086054</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1210.2445873942</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="C7" t="n">
-        <v>1336.246593212636</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="D7" t="n">
-        <v>1386.743548464727</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="E7" t="n">
-        <v>1386.743548464727</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="F7" t="n">
-        <v>1386.743548464727</v>
+        <v>700.1293446184156</v>
       </c>
       <c r="G7" t="n">
-        <v>1386.743548464727</v>
+        <v>853.7180055872682</v>
       </c>
       <c r="H7" t="n">
-        <v>1386.743548464727</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="I7" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J7" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T7" t="n">
-        <v>218.7737217817557</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U7" t="n">
-        <v>465.3348468790587</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="V7" t="n">
-        <v>664.1562397650047</v>
+        <v>403.8774537668028</v>
       </c>
       <c r="W7" t="n">
-        <v>836.0471580246821</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="X7" t="n">
-        <v>987.0779490488756</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="Y7" t="n">
-        <v>1098.487249727908</v>
+        <v>575.7683720264802</v>
       </c>
     </row>
     <row r="8">
@@ -4795,25 +4795,25 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>400.18</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
-        <v>464.2419149748744</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="M8" t="n">
-        <v>834.5019149748744</v>
+        <v>1192.338330351759</v>
       </c>
       <c r="N8" t="n">
-        <v>1204.761914974874</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>1204.761914974874</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P8" t="n">
-        <v>1262.853806841132</v>
+        <v>1496</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108.369257226991</v>
+        <v>746.1195952961839</v>
       </c>
       <c r="C9" t="n">
-        <v>108.369257226991</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="D9" t="n">
-        <v>108.369257226991</v>
+        <v>29.92</v>
       </c>
       <c r="E9" t="n">
-        <v>108.369257226991</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
-        <v>108.369257226991</v>
+        <v>29.92</v>
       </c>
       <c r="G9" t="n">
-        <v>108.369257226991</v>
+        <v>29.92</v>
       </c>
       <c r="H9" t="n">
-        <v>108.369257226991</v>
+        <v>29.92</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1357.784024336592</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S9" t="n">
-        <v>1294.664012937232</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T9" t="n">
-        <v>916.8862351594544</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U9" t="n">
-        <v>916.6883303130679</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V9" t="n">
-        <v>538.9105525352901</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W9" t="n">
-        <v>506.210408181928</v>
+        <v>1096.051174953908</v>
       </c>
       <c r="X9" t="n">
-        <v>486.1470350047688</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y9" t="n">
-        <v>486.1470350047688</v>
+        <v>1075.987801776748</v>
       </c>
     </row>
     <row r="10">
@@ -4929,16 +4929,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1142.912638434878</v>
+        <v>905.2325217179426</v>
       </c>
       <c r="C10" t="n">
-        <v>1268.914644253314</v>
+        <v>1031.234527536378</v>
       </c>
       <c r="D10" t="n">
-        <v>1268.914644253314</v>
+        <v>1144.553671661379</v>
       </c>
       <c r="E10" t="n">
-        <v>1386.743548464727</v>
+        <v>1262.382575872791</v>
       </c>
       <c r="F10" t="n">
         <v>1386.743548464727</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>151.441772822434</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="U10" t="n">
-        <v>398.002897919737</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="V10" t="n">
-        <v>596.8242908056829</v>
+        <v>664.1562397650047</v>
       </c>
       <c r="W10" t="n">
-        <v>768.7152090653603</v>
+        <v>836.0471580246821</v>
       </c>
       <c r="X10" t="n">
-        <v>919.7460000895538</v>
+        <v>905.2325217179426</v>
       </c>
       <c r="Y10" t="n">
-        <v>1031.155300768586</v>
+        <v>905.2325217179426</v>
       </c>
     </row>
     <row r="11">
@@ -5035,19 +5035,19 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L11" t="n">
-        <v>523.631587033441</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M11" t="n">
-        <v>1166.141587033441</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N11" t="n">
-        <v>1310.98</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O11" t="n">
-        <v>1953.49</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P11" t="n">
         <v>2596</v>
@@ -5056,13 +5056,13 @@
         <v>2596</v>
       </c>
       <c r="R11" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S11" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U11" t="n">
         <v>1858.092802114017</v>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>168.4528527561725</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C12" t="n">
         <v>127.9478906899915</v>
@@ -5141,22 +5141,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T12" t="n">
-        <v>1522.440726853217</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U12" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V12" t="n">
-        <v>1348.024214018445</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W12" t="n">
-        <v>911.2836656246791</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X12" t="n">
-        <v>487.1798884071159</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y12" t="n">
-        <v>232.6513948231691</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="13">
@@ -5272,16 +5272,16 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K14" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L14" t="n">
-        <v>950.0896384907273</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M14" t="n">
-        <v>1114.38799366138</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N14" t="n">
-        <v>1756.89799366138</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O14" t="n">
         <v>2399.40799366138</v>
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1141.180125483445</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C15" t="n">
-        <v>776.43273917484</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D15" t="n">
-        <v>424.9805301872615</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E15" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F15" t="n">
         <v>60.0226114399994</v>
@@ -5433,19 +5433,19 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L16" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M16" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N16" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O16" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P16" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q16" t="n">
         <v>464.3167555675508</v>
@@ -5494,13 +5494,13 @@
         <v>292.9013723451099</v>
       </c>
       <c r="F17" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G17" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H17" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
@@ -5512,19 +5512,19 @@
         <v>307.5796384907274</v>
       </c>
       <c r="L17" t="n">
-        <v>523.631587033441</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M17" t="n">
-        <v>1166.141587033441</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N17" t="n">
-        <v>1808.651587033441</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O17" t="n">
-        <v>2399.40799366138</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>816.937701241021</v>
+        <v>668.0405455662462</v>
       </c>
       <c r="C18" t="n">
-        <v>776.43273917484</v>
+        <v>627.5355835000652</v>
       </c>
       <c r="D18" t="n">
-        <v>424.9805301872616</v>
+        <v>276.0833745124867</v>
       </c>
       <c r="E18" t="n">
-        <v>403.0895228924003</v>
+        <v>254.1923672176255</v>
       </c>
       <c r="F18" t="n">
-        <v>60.0226114399994</v>
+        <v>235.3678800076489</v>
       </c>
       <c r="G18" t="n">
-        <v>55.98259997866058</v>
+        <v>231.32786854631</v>
       </c>
       <c r="H18" t="n">
         <v>51.92</v>
@@ -5615,22 +5615,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T18" t="n">
-        <v>1671.337882527992</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U18" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V18" t="n">
-        <v>1172.678945450796</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W18" t="n">
-        <v>1060.180821299454</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X18" t="n">
-        <v>960.3194683243149</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y18" t="n">
-        <v>881.1362433080176</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="19">
@@ -5670,22 +5670,22 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M19" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N19" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O19" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R19" t="n">
         <v>82.79157247680381</v>
@@ -5731,7 +5731,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F20" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G20" t="n">
         <v>125.5027119537179</v>
@@ -5743,25 +5743,25 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L20" t="n">
-        <v>949.6332762537361</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M20" t="n">
-        <v>1592.143276253736</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="N20" t="n">
-        <v>1651.83297330616</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="O20" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P20" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>168.4528527561725</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C21" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D21" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E21" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F21" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G21" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5852,22 +5852,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T21" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U21" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V21" t="n">
-        <v>1172.678945450796</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W21" t="n">
-        <v>735.9383970570298</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X21" t="n">
-        <v>311.8346198394665</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y21" t="n">
-        <v>232.6513948231691</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="22">
@@ -5919,13 +5919,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5956,25 +5956,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C23" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D23" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E23" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F23" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G23" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I23" t="n">
         <v>51.92</v>
@@ -5989,43 +5989,43 @@
         <v>949.6332762537361</v>
       </c>
       <c r="M23" t="n">
-        <v>1205.91497964478</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="N23" t="n">
-        <v>1205.91497964478</v>
+        <v>1310.98</v>
       </c>
       <c r="O23" t="n">
-        <v>1367.045081027735</v>
+        <v>1953.49</v>
       </c>
       <c r="P23" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S23" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W23" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X23" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.4528527561725</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C24" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D24" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E24" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F24" t="n">
         <v>60.02261143999941</v>
@@ -6092,19 +6092,19 @@
         <v>1846.683151095642</v>
       </c>
       <c r="U24" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V24" t="n">
-        <v>1172.678945450796</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W24" t="n">
-        <v>735.9383970570298</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X24" t="n">
-        <v>311.8346198394665</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.6513948231691</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="25">
@@ -6156,13 +6156,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C26" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D26" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E26" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F26" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G26" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H26" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
@@ -6220,19 +6220,19 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L26" t="n">
-        <v>523.631587033441</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M26" t="n">
-        <v>1149.849898617045</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N26" t="n">
-        <v>1792.359898617045</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O26" t="n">
-        <v>1953.49</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P26" t="n">
         <v>2596</v>
@@ -6241,28 +6241,28 @@
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S26" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X26" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="27">
@@ -6272,10 +6272,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>816.9377012410212</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C27" t="n">
-        <v>452.1903149324157</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D27" t="n">
         <v>100.7381059448373</v>
@@ -6317,31 +6317,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q27" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R27" t="n">
-        <v>1658.367018159816</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S27" t="n">
-        <v>1525.215274341931</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T27" t="n">
-        <v>1443.01795098519</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U27" t="n">
-        <v>1363.056657535792</v>
+        <v>1118.237009161395</v>
       </c>
       <c r="V27" t="n">
-        <v>1268.601438150418</v>
+        <v>699.5393655335972</v>
       </c>
       <c r="W27" t="n">
-        <v>1156.103313999076</v>
+        <v>587.0412413822553</v>
       </c>
       <c r="X27" t="n">
-        <v>1056.241961023937</v>
+        <v>487.1798884071163</v>
       </c>
       <c r="Y27" t="n">
-        <v>977.0587360076398</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="28">
@@ -6384,19 +6384,19 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M28" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N28" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O28" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P28" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R28" t="n">
         <v>82.79157247680381</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C29" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D29" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E29" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H29" t="n">
         <v>51.92</v>
@@ -6460,46 +6460,46 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L29" t="n">
-        <v>991.9887866314309</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M29" t="n">
-        <v>1009.32297330616</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N29" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O29" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P29" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>264.3753454557945</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C30" t="n">
-        <v>223.8703833896134</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D30" t="n">
-        <v>196.6605986444592</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E30" t="n">
-        <v>174.769591349598</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F30" t="n">
-        <v>155.9451041396213</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6557,28 +6557,28 @@
         <v>2164.764564500508</v>
       </c>
       <c r="R30" t="n">
-        <v>1982.60944240224</v>
+        <v>1886.686949702618</v>
       </c>
       <c r="S30" t="n">
-        <v>1849.457698584356</v>
+        <v>1753.535205884734</v>
       </c>
       <c r="T30" t="n">
-        <v>1767.260375227614</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U30" t="n">
-        <v>1687.299081778216</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V30" t="n">
-        <v>1268.601438150418</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W30" t="n">
-        <v>831.8608897566517</v>
+        <v>735.9383970570298</v>
       </c>
       <c r="X30" t="n">
-        <v>407.7571125390884</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y30" t="n">
-        <v>328.5738875227911</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="31">
@@ -6618,7 +6618,7 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M31" t="n">
         <v>1506.07469544798</v>
@@ -6633,7 +6633,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R31" t="n">
         <v>82.79157247680381</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D32" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E32" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F32" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G32" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H32" t="n">
         <v>51.92</v>
@@ -6694,49 +6694,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K32" t="n">
-        <v>307.5796384907274</v>
+        <v>310.7478922784251</v>
       </c>
       <c r="L32" t="n">
-        <v>950.0896384907273</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M32" t="n">
-        <v>1592.599638490728</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N32" t="n">
-        <v>2235.109638490728</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O32" t="n">
-        <v>2396.239739873683</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P32" t="n">
-        <v>2592.831746212303</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S32" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1316.525394051095</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C33" t="n">
-        <v>1100.675163417264</v>
+        <v>452.1903149324158</v>
       </c>
       <c r="D33" t="n">
-        <v>749.2229544296858</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E33" t="n">
         <v>403.0895228924003</v>
       </c>
       <c r="F33" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G33" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6794,28 +6794,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R33" t="n">
-        <v>2062.032218270268</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S33" t="n">
-        <v>1928.880474452383</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T33" t="n">
-        <v>1846.683151095641</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U33" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.47943340382</v>
       </c>
       <c r="V33" t="n">
-        <v>1672.26663826087</v>
+        <v>1023.781789776021</v>
       </c>
       <c r="W33" t="n">
-        <v>1559.768514109528</v>
+        <v>911.2836656246795</v>
       </c>
       <c r="X33" t="n">
-        <v>1459.907161134389</v>
+        <v>811.4223126495406</v>
       </c>
       <c r="Y33" t="n">
-        <v>1380.723936118091</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="34">
@@ -6858,7 +6858,7 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M34" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N34" t="n">
         <v>1349.248439584877</v>
@@ -6870,7 +6870,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q34" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R34" t="n">
         <v>82.79157247680381</v>
@@ -6904,37 +6904,37 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C35" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D35" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E35" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F35" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G35" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H35" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L35" t="n">
-        <v>953.2578922784251</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M35" t="n">
         <v>1595.767892278425</v>
@@ -6952,28 +6952,28 @@
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S35" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W35" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X35" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>816.937701241021</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C36" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D36" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E36" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F36" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H36" t="n">
         <v>51.92</v>
@@ -7031,28 +7031,28 @@
         <v>2164.764564500508</v>
       </c>
       <c r="R36" t="n">
-        <v>1886.686949702618</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S36" t="n">
-        <v>1753.535205884733</v>
+        <v>1525.215274341931</v>
       </c>
       <c r="T36" t="n">
-        <v>1671.337882527992</v>
+        <v>1347.095458285568</v>
       </c>
       <c r="U36" t="n">
-        <v>1591.376589078594</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V36" t="n">
-        <v>1496.92136969322</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W36" t="n">
-        <v>1384.423245541878</v>
+        <v>735.9383970570298</v>
       </c>
       <c r="X36" t="n">
-        <v>1284.561892566739</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y36" t="n">
-        <v>881.1362433080176</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="37">
@@ -7086,31 +7086,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J37" t="n">
-        <v>1515.576154611898</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K37" t="n">
-        <v>1619.080700024176</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L37" t="n">
-        <v>1608.654647405787</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M37" t="n">
-        <v>1505.227982468619</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N37" t="n">
-        <v>1348.401726605517</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O37" t="n">
-        <v>1114.295626111728</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645522</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881906</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949744347</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7168,28 +7168,28 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K38" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L38" t="n">
-        <v>950.0896384907273</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M38" t="n">
-        <v>1592.599638490728</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N38" t="n">
-        <v>2235.109638490728</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O38" t="n">
-        <v>2396.239739873683</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P38" t="n">
-        <v>2592.831746212303</v>
+        <v>2596</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
       </c>
       <c r="R38" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S38" t="n">
         <v>2451.762030971221</v>
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>168.4528527561725</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C39" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D39" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E39" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F39" t="n">
         <v>60.02261143999941</v>
@@ -7283,13 +7283,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W39" t="n">
-        <v>1384.423245541878</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X39" t="n">
-        <v>960.3194683243149</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y39" t="n">
-        <v>556.8938190655933</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="40">
@@ -7323,31 +7323,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J40" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611905</v>
       </c>
       <c r="K40" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024183</v>
       </c>
       <c r="L40" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405794</v>
       </c>
       <c r="M40" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468627</v>
       </c>
       <c r="N40" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605524</v>
       </c>
       <c r="O40" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111735</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645594</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881978</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949745075</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C41" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D41" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E41" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F41" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G41" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7405,49 +7405,49 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K41" t="n">
-        <v>1201.938527309012</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L41" t="n">
-        <v>1417.990475851726</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M41" t="n">
-        <v>2060.500475851726</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N41" t="n">
-        <v>2238.277892278425</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="O41" t="n">
-        <v>2399.40799366138</v>
+        <v>2395.783377636692</v>
       </c>
       <c r="P41" t="n">
-        <v>2596</v>
+        <v>2592.375383975311</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S41" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W41" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X41" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>588.6177696982188</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C42" t="n">
-        <v>223.8703833896134</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D42" t="n">
-        <v>196.6605986444593</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E42" t="n">
-        <v>174.769591349598</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F42" t="n">
-        <v>155.9451041396214</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G42" t="n">
-        <v>151.9050926782826</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H42" t="n">
         <v>51.92</v>
@@ -7514,19 +7514,19 @@
         <v>1767.260375227614</v>
       </c>
       <c r="U42" t="n">
-        <v>1363.056657535792</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V42" t="n">
-        <v>1268.601438150418</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W42" t="n">
-        <v>1156.103313999076</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X42" t="n">
-        <v>1056.241961023937</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y42" t="n">
-        <v>652.8163117652153</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="43">
@@ -7581,10 +7581,10 @@
         <v>819.9299076645212</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C44" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D44" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E44" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F44" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G44" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H44" t="n">
         <v>51.92</v>
@@ -7639,25 +7639,25 @@
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K44" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L44" t="n">
-        <v>950.0896384907273</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M44" t="n">
-        <v>1592.599638490728</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N44" t="n">
-        <v>2235.109638490728</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="O44" t="n">
-        <v>2396.239739873683</v>
+        <v>2395.783377636692</v>
       </c>
       <c r="P44" t="n">
-        <v>2592.831746212303</v>
+        <v>2592.375383975311</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
@@ -7675,16 +7675,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W44" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X44" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>992.2829698086708</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C45" t="n">
-        <v>951.7780077424898</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D45" t="n">
-        <v>924.5682229973356</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E45" t="n">
-        <v>578.4347914600501</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F45" t="n">
-        <v>235.3678800076491</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G45" t="n">
-        <v>231.3278685463103</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H45" t="n">
         <v>51.92</v>
@@ -7742,28 +7742,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R45" t="n">
-        <v>1737.789794027844</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S45" t="n">
-        <v>1604.638050209959</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1522.440726853217</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U45" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V45" t="n">
-        <v>1348.024214018445</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W45" t="n">
-        <v>1235.526089867104</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X45" t="n">
-        <v>1135.664736891965</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y45" t="n">
-        <v>1056.481511875667</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="46">
@@ -7818,7 +7818,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q46" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R46" t="n">
         <v>82.79157247680381</v>
@@ -7964,19 +7964,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>309.2909949748744</v>
       </c>
       <c r="M2" t="n">
         <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>778.0826666125488</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O2" t="n">
         <v>1.159015302735668</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>364.0430754681111</v>
+        <v>376.5921508449956</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>309.2909949748744</v>
       </c>
       <c r="M8" t="n">
         <v>846.2608914614127</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>652.1329472004106</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>364.0430754681111</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,22 +8678,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>376.7934807861708</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O11" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>23.48346824708341</v>
@@ -8915,19 +8915,19 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L14" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M14" t="n">
-        <v>467.3923636656659</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N14" t="n">
-        <v>879.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O14" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -9155,7 +9155,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M17" t="n">
         <v>950.4344291498551</v>
@@ -9164,13 +9164,13 @@
         <v>879.4920535472222</v>
       </c>
       <c r="O17" t="n">
-        <v>433.9659648939237</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.48346824708341</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N20" t="n">
-        <v>290.7846768324985</v>
+        <v>572.361907661023</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9632,19 +9632,19 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>560.3048366155554</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N23" t="n">
-        <v>230.4920535472222</v>
+        <v>595.4887442000139</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P23" t="n">
         <v>450.422215819576</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,13 +9863,13 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>933.9781782242026</v>
+        <v>911.3123136417682</v>
       </c>
       <c r="N26" t="n">
         <v>879.4920535472222</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>23.48346824708341</v>
@@ -10103,10 +10103,10 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M29" t="n">
-        <v>318.9437086192779</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N29" t="n">
         <v>879.4920535472222</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>3.200256351209731</v>
       </c>
       <c r="L32" t="n">
         <v>430.7657085427136</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>26.68372459829277</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,16 +10571,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L35" t="n">
-        <v>3.661228307766578</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>950.4344291498551</v>
+        <v>911.3123136417682</v>
       </c>
       <c r="N35" t="n">
         <v>879.4920535472222</v>
@@ -10811,13 +10811,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L38" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>950.4344291498551</v>
+        <v>911.3123136417682</v>
       </c>
       <c r="N38" t="n">
         <v>879.4920535472222</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>26.68372459829277</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,7 +11048,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,7 +11057,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>410.0652014529786</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.48346824708341</v>
+        <v>27.14469655484982</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,13 +11282,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>950.4344291498551</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>26.68372459829277</v>
+        <v>27.14469655484982</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23663,7 +23663,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -23903,7 +23903,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24371,7 +24371,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.8382458495973992</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24599,7 +24599,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -24614,7 +24614,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24833,10 +24833,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -25073,10 +25073,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8382458495976266</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495667287</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495595273</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25796,13 +25796,13 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26018,7 +26018,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8382458495976817</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -26296,10 +26296,10 @@
         <v>1290840.845493009</v>
       </c>
       <c r="K2" t="n">
+        <v>1290840.84549301</v>
+      </c>
+      <c r="L2" t="n">
         <v>1290840.845493009</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1290840.84549301</v>
       </c>
       <c r="M2" t="n">
         <v>1290840.84549301</v>
@@ -26308,7 +26308,7 @@
         <v>1290840.84549301</v>
       </c>
       <c r="O2" t="n">
-        <v>1290840.84549301</v>
+        <v>1290840.845493009</v>
       </c>
       <c r="P2" t="n">
         <v>1290840.84549301</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570963.5697337883</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634526</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.979796175</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259448</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216768</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497197</v>
+        <v>469921.3886193652</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286018</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301392</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>423708.1316741448</v>
+        <v>430209.4966071217</v>
       </c>
       <c r="C6" t="n">
-        <v>656815.0538616335</v>
+        <v>663316.4187946102</v>
       </c>
       <c r="D6" t="n">
-        <v>658826.7012774575</v>
+        <v>665328.0662104344</v>
       </c>
       <c r="E6" t="n">
-        <v>137407.316696835</v>
+        <v>143870.3078271897</v>
       </c>
       <c r="F6" t="n">
-        <v>728643.379515058</v>
+        <v>735106.3706454121</v>
       </c>
       <c r="G6" t="n">
-        <v>730331.7690367107</v>
+        <v>736794.7601670654</v>
       </c>
       <c r="H6" t="n">
-        <v>732022.5019466736</v>
+        <v>738485.4930770274</v>
       </c>
       <c r="I6" t="n">
-        <v>733715.5951472202</v>
+        <v>740178.5862775744</v>
       </c>
       <c r="J6" t="n">
-        <v>346963.0657621444</v>
+        <v>353426.0568924989</v>
       </c>
       <c r="K6" t="n">
-        <v>737108.9311409782</v>
+        <v>743571.9222713333</v>
       </c>
       <c r="L6" t="n">
-        <v>738809.208863323</v>
+        <v>745272.1999936765</v>
       </c>
       <c r="M6" t="n">
-        <v>643711.9167432905</v>
+        <v>650174.9078736448</v>
       </c>
       <c r="N6" t="n">
-        <v>742217.0728340541</v>
+        <v>748680.0639644087</v>
       </c>
       <c r="O6" t="n">
-        <v>487124.6954325162</v>
+        <v>493587.6865628702</v>
       </c>
       <c r="P6" t="n">
-        <v>745634.8030841</v>
+        <v>752097.7942144541</v>
       </c>
     </row>
   </sheetData>
@@ -26993,22 +26993,22 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>321</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>-0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>321</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27106,7 +27106,7 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27566,10 +27566,10 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>112.1969504430963</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>26.1959257979226</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27578,10 +27578,10 @@
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>229.534809722118</v>
       </c>
       <c r="Y3" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27591,31 +27591,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>22.26478490148153</v>
+        <v>345.7735384887769</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27645,13 +27645,13 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>246.1248309835077</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27752,7 +27752,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27803,22 +27803,22 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
+        <v>296.0461165352868</v>
+      </c>
+      <c r="U6" t="n">
         <v>400</v>
-      </c>
-      <c r="U6" t="n">
-        <v>26.1959257979226</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
       </c>
       <c r="W6" t="n">
+        <v>58.37314290982852</v>
+      </c>
+      <c r="X6" t="n">
         <v>400</v>
       </c>
-      <c r="X6" t="n">
-        <v>45.86273944538755</v>
-      </c>
       <c r="Y6" t="n">
-        <v>91.7256037638432</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="7">
@@ -27828,37 +27828,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>336.5432435627184</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>345.3117811607983</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.55655664632661</v>
+        <v>57.98703223056765</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28007,7 +28007,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>131.9078476517218</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,13 +28040,13 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>30.47344446279683</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28065,19 +28065,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>244.8599384153005</v>
@@ -28116,10 +28116,10 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>359.1680042930194</v>
+      </c>
+      <c r="T10" t="n">
         <v>400</v>
-      </c>
-      <c r="T10" t="n">
-        <v>291.1559346371388</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
@@ -28131,10 +28131,10 @@
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>317.3278511808758</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28201,7 +28201,7 @@
         <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="V11" t="n">
         <v>321</v>
@@ -28223,10 +28223,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>321</v>
@@ -28277,7 +28277,7 @@
         <v>321</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U12" t="n">
         <v>321</v>
@@ -28286,13 +28286,13 @@
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="Y12" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -28460,11 +28460,11 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>321</v>
+      </c>
+      <c r="C15" t="n">
         <v>147.4081841180271</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
@@ -28472,7 +28472,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28630,7 +28630,7 @@
         <v>321</v>
       </c>
       <c r="F17" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G17" t="n">
         <v>321</v>
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>321</v>
@@ -28709,13 +28709,13 @@
         <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
       </c>
       <c r="H18" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="I18" t="n">
         <v>191.6509141932353</v>
@@ -28751,7 +28751,7 @@
         <v>321</v>
       </c>
       <c r="T18" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="U18" t="n">
         <v>321</v>
@@ -28937,16 +28937,16 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28991,16 +28991,16 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y21" t="n">
         <v>321</v>
@@ -29113,7 +29113,7 @@
         <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C24" t="n">
         <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29228,16 +29228,16 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
         <v>321</v>
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29408,13 +29408,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>226.0367322273741</v>
+        <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E27" t="n">
         <v>321</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -29465,10 +29465,10 @@
         <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>321</v>
@@ -29477,7 +29477,7 @@
         <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>321</v>
+        <v>147.4081841180266</v>
       </c>
     </row>
     <row r="28">
@@ -29584,7 +29584,7 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I29" t="n">
         <v>96.76634561233286</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29660,7 +29660,7 @@
         <v>321</v>
       </c>
       <c r="G30" t="n">
-        <v>226.0367322273743</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>321</v>
@@ -29693,7 +29693,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="S30" t="n">
         <v>321</v>
@@ -29711,7 +29711,7 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="n">
         <v>321</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
         <v>96.76634561233286</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29885,13 +29885,13 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -29930,7 +29930,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>321</v>
@@ -29942,7 +29942,7 @@
         <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>321</v>
@@ -29951,7 +29951,7 @@
         <v>321</v>
       </c>
       <c r="Y33" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
     </row>
     <row r="34">
@@ -30061,7 +30061,7 @@
         <v>321</v>
       </c>
       <c r="I35" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30128,10 +30128,10 @@
         <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G36" t="n">
         <v>321</v>
@@ -30167,13 +30167,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>226.0367322273739</v>
+        <v>321</v>
       </c>
       <c r="S36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="U36" t="n">
         <v>321</v>
@@ -30182,13 +30182,13 @@
         <v>321</v>
       </c>
       <c r="W36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37">
@@ -30222,7 +30222,7 @@
         <v>321</v>
       </c>
       <c r="J37" t="n">
-        <v>321.0000000000312</v>
+        <v>321</v>
       </c>
       <c r="K37" t="n">
         <v>321</v>
@@ -30325,10 +30325,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S38" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T38" t="n">
         <v>321</v>
@@ -30356,19 +30356,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C39" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
@@ -30419,13 +30419,13 @@
         <v>321</v>
       </c>
       <c r="W39" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40">
@@ -30459,7 +30459,7 @@
         <v>321</v>
       </c>
       <c r="J40" t="n">
-        <v>321</v>
+        <v>321.0000000000386</v>
       </c>
       <c r="K40" t="n">
         <v>321</v>
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30596,10 +30596,10 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>321</v>
@@ -30611,7 +30611,7 @@
         <v>321</v>
       </c>
       <c r="H42" t="n">
-        <v>226.0367322273742</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>191.6509141932353</v>
@@ -30650,19 +30650,19 @@
         <v>321</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="W42" t="n">
         <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43">
@@ -30769,7 +30769,7 @@
         <v>321</v>
       </c>
       <c r="H44" t="n">
-        <v>320.5394126346856</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I44" t="n">
         <v>96.76634561233286</v>
@@ -30833,10 +30833,10 @@
         <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -30848,7 +30848,7 @@
         <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="I45" t="n">
         <v>191.6509141932353</v>
@@ -30878,7 +30878,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S45" t="n">
         <v>321</v>
@@ -34743,19 +34743,19 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
+        <v>52.15992964824119</v>
+      </c>
+      <c r="L2" t="n">
         <v>374</v>
-      </c>
-      <c r="L2" t="n">
-        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>235.5012052109774</v>
+        <v>248.0502805878619</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,31 +34877,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>228.8979542159473</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>323.5087535872954</v>
       </c>
       <c r="K4" t="n">
         <v>132.8490622644307</v>
@@ -34931,13 +34931,13 @@
         <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
-        <v>36.88616611659423</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -35114,37 +35114,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>51.00702550716294</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T7" t="n">
         <v>190.7613351330866</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>146.1414709445821</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
+        <v>52.15992964824119</v>
+      </c>
+      <c r="L8" t="n">
         <v>374</v>
-      </c>
-      <c r="L8" t="n">
-        <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
         <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>248.0502805878619</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,19 +35351,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -35402,10 +35402,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>81.91726977022537</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U10" t="n">
         <v>249.0516415124273</v>
@@ -35417,10 +35417,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>69.88420575076826</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35457,22 +35457,22 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L11" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M11" t="n">
         <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>146.3014272389487</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O11" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P11" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35694,19 +35694,19 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K14" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L14" t="n">
         <v>649</v>
       </c>
       <c r="M14" t="n">
-        <v>165.9579345158109</v>
+        <v>649</v>
       </c>
       <c r="N14" t="n">
-        <v>649</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O14" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P14" t="n">
         <v>198.5777841804241</v>
@@ -35934,7 +35934,7 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L17" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M17" t="n">
         <v>649</v>
@@ -35943,13 +35943,13 @@
         <v>649</v>
       </c>
       <c r="O17" t="n">
-        <v>596.7236430585247</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P17" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>341.8698541138008</v>
+      </c>
+      <c r="O20" t="n">
         <v>649</v>
-      </c>
-      <c r="N20" t="n">
-        <v>60.29262328527629</v>
-      </c>
-      <c r="O20" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P20" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36317,7 +36317,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H22" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I22" t="n">
         <v>163.0214951995539</v>
@@ -36411,19 +36411,19 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M23" t="n">
-        <v>258.8704074657004</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>364.9966906527918</v>
       </c>
       <c r="O23" t="n">
-        <v>162.757678164601</v>
+        <v>649</v>
       </c>
       <c r="P23" t="n">
         <v>649</v>
       </c>
       <c r="Q23" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36642,13 +36642,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L26" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
-        <v>632.5437490743476</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="N26" t="n">
         <v>649</v>
@@ -36657,7 +36657,7 @@
         <v>162.757678164601</v>
       </c>
       <c r="P26" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36882,10 +36882,10 @@
         <v>649</v>
       </c>
       <c r="L29" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M29" t="n">
-        <v>17.50927946942293</v>
+        <v>179.1121759491996</v>
       </c>
       <c r="N29" t="n">
         <v>649</v>
@@ -36897,7 +36897,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37116,7 +37116,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K32" t="n">
-        <v>175.9119195979899</v>
+        <v>179.1121759491997</v>
       </c>
       <c r="L32" t="n">
         <v>649</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.200256351209361</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37265,7 +37265,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H34" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I34" t="n">
         <v>163.0214951995539</v>
@@ -37350,16 +37350,16 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L35" t="n">
-        <v>221.895519765053</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M35" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="N35" t="n">
         <v>649</v>
@@ -37502,13 +37502,13 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
       </c>
       <c r="J37" t="n">
-        <v>329.5882314919923</v>
+        <v>329.5882314919611</v>
       </c>
       <c r="K37" t="n">
         <v>104.5500458709881</v>
@@ -37590,13 +37590,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K38" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L38" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="N38" t="n">
         <v>649</v>
@@ -37608,7 +37608,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.200256351209361</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>163.0214951995539</v>
       </c>
       <c r="J40" t="n">
-        <v>329.5882314919611</v>
+        <v>329.5882314919997</v>
       </c>
       <c r="K40" t="n">
         <v>104.5500458709881</v>
@@ -37827,7 +37827,7 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K41" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L41" t="n">
         <v>218.2342914572864</v>
@@ -37836,7 +37836,7 @@
         <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>179.5731479057565</v>
+        <v>649</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.661228307766413</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K44" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L44" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
         <v>649</v>
@@ -38082,7 +38082,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.200256351209361</v>
+        <v>3.661228307766413</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
